--- a/KPI-details.xlsx
+++ b/KPI-details.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ntpccoin-my.sharepoint.com/personal/abhilashkaimal_ntpc_co_in/Documents/Patratu/Project Dashboard - Microsoft/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="31" documentId="13_ncr:1_{29C74D10-F176-41A0-A003-C2CD4B9FEB0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EABAE085-EC52-4FD5-8259-B2B690583460}"/>
+  <xr:revisionPtr revIDLastSave="38" documentId="13_ncr:1_{29C74D10-F176-41A0-A003-C2CD4B9FEB0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5841E357-3909-4EF0-8A94-CC9CAA8ACCBA}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -142,10 +142,10 @@
     <t>60 P91/92 joints in Unit 3. Aug achievement was - 26</t>
   </si>
   <si>
-    <t>ST 2 Chraging - 15.09.26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1st HT Switchgear charging in Unit 3 </t>
+    <t>1st HT Switchgear charging in Unit 3 - Completed</t>
+  </si>
+  <si>
+    <t>ST 2 Charging - 15.09.26/25.09.26</t>
   </si>
 </sst>
 </file>
@@ -250,10 +250,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -577,7 +573,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.45">
@@ -593,7 +589,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.45">
@@ -790,14 +786,14 @@
         <v>15</v>
       </c>
       <c r="C10" s="4">
-        <v>10244</v>
+        <v>10690</v>
       </c>
       <c r="D10" s="2">
         <v>10820</v>
       </c>
       <c r="E10" s="3">
         <f t="shared" si="0"/>
-        <v>0.94676524953789276</v>
+        <v>0.98798521256931604</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15.75" x14ac:dyDescent="0.5">
@@ -844,15 +840,14 @@
         <v>19</v>
       </c>
       <c r="C13" s="2">
-        <v>2047</v>
+        <v>1644</v>
       </c>
       <c r="D13" s="2">
-        <f>4806.8+529</f>
-        <v>5335.8</v>
+        <v>5309</v>
       </c>
       <c r="E13" s="3">
         <f t="shared" si="0"/>
-        <v>0.38363506878068893</v>
+        <v>0.30966283669240913</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="15.75" x14ac:dyDescent="0.5">
@@ -863,14 +858,14 @@
         <v>20</v>
       </c>
       <c r="C14" s="2">
-        <v>10656</v>
+        <v>11284</v>
       </c>
       <c r="D14" s="2">
         <v>14724</v>
       </c>
       <c r="E14" s="3">
         <f t="shared" si="0"/>
-        <v>0.72371638141809291</v>
+        <v>0.76636783482749249</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="15.75" x14ac:dyDescent="0.5">
@@ -881,14 +876,14 @@
         <v>21</v>
       </c>
       <c r="C15" s="2">
-        <v>3338</v>
+        <v>4615</v>
       </c>
       <c r="D15" s="2">
         <v>10800</v>
       </c>
       <c r="E15" s="3">
         <f t="shared" si="0"/>
-        <v>0.30907407407407406</v>
+        <v>0.42731481481481481</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="15.75" x14ac:dyDescent="0.5">

--- a/KPI-details.xlsx
+++ b/KPI-details.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">

--- a/KPI-details.xlsx
+++ b/KPI-details.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ntpccoin-my.sharepoint.com/personal/abhilashkaimal_ntpc_co_in/Documents/Patratu/Project Dashboard - Microsoft/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="38" documentId="13_ncr:1_{29C74D10-F176-41A0-A003-C2CD4B9FEB0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5841E357-3909-4EF0-8A94-CC9CAA8ACCBA}"/>
+  <xr:revisionPtr revIDLastSave="43" documentId="13_ncr:1_{29C74D10-F176-41A0-A003-C2CD4B9FEB0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9776AF0B-B7ED-4845-9A98-B68F75BB375F}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SepTargets" sheetId="3" r:id="rId1"/>
@@ -133,19 +133,19 @@
     <t>Boiler DHT - 10.08.26- Completed on 17.08.26</t>
   </si>
   <si>
-    <t>PA Fan foundation casting completion</t>
-  </si>
-  <si>
-    <t>Start of ash handling works in Unit 3</t>
-  </si>
-  <si>
-    <t>60 P91/92 joints in Unit 3. Aug achievement was - 26</t>
-  </si>
-  <si>
-    <t>1st HT Switchgear charging in Unit 3 - Completed</t>
-  </si>
-  <si>
-    <t>ST 2 Charging - 15.09.26/25.09.26</t>
+    <t>FD Fan foundation casting completion</t>
+  </si>
+  <si>
+    <t>All HT switchgear charging of Unit 3</t>
+  </si>
+  <si>
+    <t>ST 2 and UAT3 charging</t>
+  </si>
+  <si>
+    <t>60 P91/92 joints in Unit 3. Sep achievement was - 28</t>
+  </si>
+  <si>
+    <t>Start of BAIM silo erection in Unit 3</t>
   </si>
 </sst>
 </file>
@@ -538,13 +538,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98AE43AB-79A9-48E8-BCBE-F2658EB23C7E}">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>23</v>
       </c>
@@ -552,7 +552,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -560,7 +560,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -568,36 +568,36 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -608,7 +608,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E16"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
@@ -617,7 +617,7 @@
     <col min="5" max="5" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -634,7 +634,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -652,7 +652,7 @@
         <v>0.98481135875402792</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -670,7 +670,7 @@
         <v>0.97284352698884047</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -688,7 +688,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -706,7 +706,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -724,7 +724,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -742,7 +742,7 @@
         <v>0.97232748304746708</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -760,7 +760,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -778,7 +778,7 @@
         <v>0.98255124512959513</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -796,7 +796,7 @@
         <v>0.98798521256931604</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -814,7 +814,7 @@
         <v>0.99589552238805967</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>17</v>
       </c>
@@ -832,7 +832,7 @@
         <v>0.61516206319786626</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -850,7 +850,7 @@
         <v>0.30966283669240913</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -868,7 +868,7 @@
         <v>0.76636783482749249</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>17</v>
       </c>
@@ -886,7 +886,7 @@
         <v>0.42731481481481481</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -912,13 +912,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>23</v>
       </c>
@@ -926,7 +926,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -934,7 +934,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -942,7 +942,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -950,7 +950,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -958,7 +958,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -966,7 +966,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>

--- a/KPI-details.xlsx
+++ b/KPI-details.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ntpccoin-my.sharepoint.com/personal/abhilashkaimal_ntpc_co_in/Documents/Patratu/Project Dashboard - Microsoft/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="43" documentId="13_ncr:1_{29C74D10-F176-41A0-A003-C2CD4B9FEB0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9776AF0B-B7ED-4845-9A98-B68F75BB375F}"/>
+  <xr:revisionPtr revIDLastSave="46" documentId="13_ncr:1_{29C74D10-F176-41A0-A003-C2CD4B9FEB0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7B3CFC2A-CFA0-42D4-9080-38AFF7CE8832}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SepTargets" sheetId="3" r:id="rId1"/>
@@ -750,14 +750,14 @@
         <v>13</v>
       </c>
       <c r="C8" s="2">
-        <v>17940</v>
+        <v>18741</v>
       </c>
       <c r="D8" s="2">
-        <v>17940</v>
+        <v>18087</v>
       </c>
       <c r="E8" s="3">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>1.0361585669265219</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
@@ -804,14 +804,14 @@
         <v>16</v>
       </c>
       <c r="C11" s="2">
-        <v>13345</v>
+        <v>13293</v>
       </c>
       <c r="D11" s="2">
         <v>13400</v>
       </c>
       <c r="E11" s="3">
         <f t="shared" si="0"/>
-        <v>0.99589552238805967</v>
+        <v>0.99201492537313429</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
